--- a/data/trans_orig/P6904-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6904-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70558</t>
+          <t>69578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89969</t>
+          <t>89493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89138</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112833</t>
+          <t>113474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21317</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>41708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36021</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59716</t>
+          <t>59035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126718</t>
+          <t>125114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161042</t>
+          <t>161134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>59169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81089</t>
+          <t>79731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194089</t>
+          <t>192566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233513</t>
+          <t>233895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125903</t>
+          <t>125811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160227</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>38840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>59402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172002</t>
+          <t>171620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211426</t>
+          <t>212949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32121</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>31350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36083</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58697</t>
+          <t>58507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41954</t>
+          <t>43069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58657</t>
+          <t>58565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32587</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48255</t>
+          <t>48085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79361</t>
+          <t>79551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101975</t>
+          <t>102762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223693</t>
+          <t>222390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268198</t>
+          <t>267606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100160</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129872</t>
+          <t>128347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333659</t>
+          <t>334291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386773</t>
+          <t>387206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204107</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248612</t>
+          <t>249915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>91774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119961</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305654</t>
+          <t>305221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358768</t>
+          <t>358136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>26549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41580</t>
+          <t>40906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43575</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62907</t>
+          <t>63562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>31155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32731</t>
+          <t>32076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52063</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109053</t>
+          <t>108453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138929</t>
+          <t>139592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64768</t>
+          <t>65363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87285</t>
+          <t>88860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181839</t>
+          <t>183125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>221808</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81774</t>
+          <t>81111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111650</t>
+          <t>112250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43245</t>
+          <t>41670</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65762</t>
+          <t>65167</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>129426</t>
+          <t>131461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169395</t>
+          <t>168109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>26179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22102</t>
+          <t>21129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42757</t>
+          <t>42490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>24067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>37384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48528</t>
+          <t>48795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67559</t>
+          <t>67904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159330</t>
+          <t>158291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196140</t>
+          <t>196569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94801</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124703</t>
+          <t>125458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264294</t>
+          <t>264105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310550</t>
+          <t>310470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128356</t>
+          <t>127927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165166</t>
+          <t>166205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88958</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118860</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227607</t>
+          <t>227687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273863</t>
+          <t>274052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>23212</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38282</t>
+          <t>39253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51312</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32159</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>22738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>130172</t>
+          <t>130490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160683</t>
+          <t>161344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81892</t>
+          <t>82844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100846</t>
+          <t>101658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>220911</t>
+          <t>219484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257563</t>
+          <t>255203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68699</t>
+          <t>68038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99210</t>
+          <t>98892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>22907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42673</t>
+          <t>41721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96384</t>
+          <t>98744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133036</t>
+          <t>134463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22699</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39491</t>
+          <t>39493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32424</t>
+          <t>32969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>50738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59805</t>
+          <t>60428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84431</t>
+          <t>84108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24037</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>40431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>53128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77431</t>
+          <t>76808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187710</t>
+          <t>187557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>226036</t>
+          <t>226433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131567</t>
+          <t>131790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159313</t>
+          <t>158949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>325792</t>
+          <t>329246</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>374931</t>
+          <t>374833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,37%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122455</t>
+          <t>122058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160781</t>
+          <t>160934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56985</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84731</t>
+          <t>84508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189857</t>
+          <t>189955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238996</t>
+          <t>235542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>17472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26498</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>34387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46684</t>
+          <t>47096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132341</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164322</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>149239</t>
+          <t>148050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>196259</t>
+          <t>190573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>291300</t>
+          <t>289841</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>349489</t>
+          <t>350350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75258</t>
+          <t>75456</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107239</t>
+          <t>108290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42109</t>
+          <t>47795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>90318</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>127598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186648</t>
+          <t>188107</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46080</t>
+          <t>45954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36440</t>
+          <t>38320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54864</t>
+          <t>55068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>72157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94280</t>
+          <t>96719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41667</t>
+          <t>42341</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35831</t>
+          <t>35627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54255</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65941</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89694</t>
+          <t>88064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186934</t>
+          <t>188451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225889</t>
+          <t>226652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>210361</t>
+          <t>210286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263187</t>
+          <t>264360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409856</t>
+          <t>410245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>481090</t>
+          <t>479483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112431</t>
+          <t>111668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151386</t>
+          <t>149869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90862</t>
+          <t>89689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>143688</t>
+          <t>143763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211279</t>
+          <t>212886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>282513</t>
+          <t>282124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
